--- a/assets/factor/practice/Regression Questions - ANOVA Problem Set 5.xlsx
+++ b/assets/factor/practice/Regression Questions - ANOVA Problem Set 5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox (Personal)\Courses\Teaching\FIN 203\FIN 203 Fall 2020\S3 Online\assets\factor\practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{252FE607-6779-4CC0-A8F6-E9D01E942EA4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA5FA992-3522-488A-8936-761300857156}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{8DCDFA2E-5CA9-465E-B789-4F49B614B1AD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{8DCDFA2E-5CA9-465E-B789-4F49B614B1AD}"/>
   </bookViews>
   <sheets>
     <sheet name="Question" sheetId="10" r:id="rId1"/>
@@ -758,7 +758,7 @@
       </c>
       <c r="B5" s="8">
         <f>C12/C14</f>
-        <v>0.64749999999999996</v>
+        <v>0.56499999999999995</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -767,7 +767,7 @@
       </c>
       <c r="B6" s="8">
         <f>1-C13/C14*B14/B13</f>
-        <v>0.62874999999999992</v>
+        <v>0.55374999999999996</v>
       </c>
       <c r="E6" s="13"/>
     </row>
@@ -820,15 +820,15 @@
       </c>
       <c r="C12" s="11">
         <f>C14-C13</f>
-        <v>5180</v>
+        <v>4520</v>
       </c>
       <c r="D12" s="11">
         <f>C12/B12</f>
-        <v>1726.6666666666667</v>
+        <v>1506.6666666666667</v>
       </c>
       <c r="E12" s="8">
         <f>D12/D13</f>
-        <v>57.555555555555557</v>
+        <v>50.222222222222221</v>
       </c>
       <c r="F12" s="8">
         <f>1-_xlfn.F.DIST(E12,B12,B13,TRUE)</f>
@@ -840,11 +840,12 @@
         <v>8</v>
       </c>
       <c r="B13" s="1">
-        <v>94</v>
+        <f>B8-(B12+1)</f>
+        <v>116</v>
       </c>
       <c r="C13" s="11">
         <f>D13*B13</f>
-        <v>2820</v>
+        <v>3480</v>
       </c>
       <c r="D13" s="11">
         <v>30</v>
@@ -857,7 +858,8 @@
         <v>9</v>
       </c>
       <c r="B14" s="2">
-        <v>99</v>
+        <f>B8-1</f>
+        <v>119</v>
       </c>
       <c r="C14" s="12">
         <v>8000</v>
